--- a/public/template-kondisi-ruangan.xlsx
+++ b/public/template-kondisi-ruangan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\diakademik\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61A5BA96-DC56-45BA-A55C-B42DD41F0CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9410084-5409-40C7-B3D3-30ABE4E07271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{478F510C-263C-485C-9031-C9B0FD6F61CB}"/>
   </bookViews>
@@ -23,11 +23,8 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -46,9 +43,6 @@
     <t>Keterangan</t>
   </si>
   <si>
-    <t>D1001</t>
-  </si>
-  <si>
     <t>Kerusakan Kusen (%)</t>
   </si>
   <si>
@@ -56,6 +50,9 @@
   </si>
   <si>
     <t>slot pintu rusak</t>
+  </si>
+  <si>
+    <t>DAPUR</t>
   </si>
 </sst>
 </file>
@@ -118,7 +115,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -431,7 +428,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -439,16 +436,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
